--- a/13772_Cuenca_Chicama/_raw_reportes_xlsx/IDConfig_67590_completo.xlsx
+++ b/13772_Cuenca_Chicama/_raw_reportes_xlsx/IDConfig_67590_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rb50d735a1a2f4bbe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rb4786e8a0d81404d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -174,7 +174,7 @@
       </x:c>
       <x:c s="" t="inlineStr">
         <x:is>
-          <x:t>Dpto: La Libertad / Prov: Gran Chimu / Dist.: Lucma</x:t>
+          <x:t>Dpto: La Libertad / Prov: Gran Chimú / Dist.: Lucma</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -255,6 +255,111 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0135</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0135</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.1441</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.1441</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.1441</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.1441</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.1441</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>
@@ -264,7 +369,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.4777</x:v>
+        <x:v>      3.1441</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -279,7 +384,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.4777</x:v>
+        <x:v>      2.7610</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -294,7 +399,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.6066</x:v>
+        <x:v>      3.2777</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -309,7 +414,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.6066</x:v>
+        <x:v>      3.2777</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -324,7 +429,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.6066</x:v>
+        <x:v>      3.2777</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -339,7 +444,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.6066</x:v>
+        <x:v>      3.2777</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -354,7 +459,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.6066</x:v>
+        <x:v>      3.2777</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -369,7 +474,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.7395</x:v>
+        <x:v>      3.4141</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -384,7 +489,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.7395</x:v>
+        <x:v>      3.4141</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -399,7 +504,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.7395</x:v>
+        <x:v>      3.4141</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -414,7 +519,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.8761</x:v>
+        <x:v>      3.4141</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -429,7 +534,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.8761</x:v>
+        <x:v>      3.4141</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -444,7 +549,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.0167</x:v>
+        <x:v>      3.4141</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -459,7 +564,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.0167</x:v>
+        <x:v>      3.4141</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -474,7 +579,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.0167</x:v>
+        <x:v>      3.4141</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -489,7 +594,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.3098</x:v>
+        <x:v>      3.5535</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -504,7 +609,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.3098</x:v>
+        <x:v>      3.5535</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -519,7 +624,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.3098</x:v>
+        <x:v>      3.5535</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -534,7 +639,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.3098</x:v>
+        <x:v>      3.5535</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -549,7 +654,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.3098</x:v>
+        <x:v>      3.5535</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -564,7 +669,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.4623</x:v>
+        <x:v>      3.6957</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -579,7 +684,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.4623</x:v>
+        <x:v>      3.6957</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -594,7 +699,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.4623</x:v>
+        <x:v>      3.6957</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -609,7 +714,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.4623</x:v>
+        <x:v>      3.6957</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -624,7 +729,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.6188</x:v>
+        <x:v>      3.8409</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -639,7 +744,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.6188</x:v>
+        <x:v>      3.8409</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -654,7 +759,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.6188</x:v>
+        <x:v>      3.8409</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -669,7 +774,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.6188</x:v>
+        <x:v>      3.8409</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -684,7 +789,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.6188</x:v>
+        <x:v>      3.8409</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -699,7 +804,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.7795</x:v>
+        <x:v>      3.9891</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -714,7 +819,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.7795</x:v>
+        <x:v>      3.9891</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -729,7 +834,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.9442</x:v>
+        <x:v>      4.1402</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -744,7 +849,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.9442</x:v>
+        <x:v>      4.1402</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -759,7 +864,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.9442</x:v>
+        <x:v>      4.1402</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -774,7 +879,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.1130</x:v>
+        <x:v>      4.2942</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -789,7 +894,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.1130</x:v>
+        <x:v>      4.2942</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -804,7 +909,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.1130</x:v>
+        <x:v>      4.2942</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -819,7 +924,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.2860</x:v>
+        <x:v>      4.4512</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -834,7 +939,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.2860</x:v>
+        <x:v>      4.4512</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -849,7 +954,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.2860</x:v>
+        <x:v>      4.4512</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -864,7 +969,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.2860</x:v>
+        <x:v>      4.4512</x:v>
       </x:c>
     </x:row>
     <x:row>

--- a/13772_Cuenca_Chicama/_raw_reportes_xlsx/IDConfig_67590_completo.xlsx
+++ b/13772_Cuenca_Chicama/_raw_reportes_xlsx/IDConfig_67590_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rb4786e8a0d81404d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rd803731af4b64677"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,711 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.1800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.1800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.1800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.1800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.1800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.2905</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.2905</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.2905</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.2905</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.2905</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.2905</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.2905</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.2905</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.2905</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.2905</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.2905</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.4038</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.4038</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.4038</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.5200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.5200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.5200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.5200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.5200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.6390</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.6390</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.6390</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.6390</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.6390</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.6390</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.6390</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.6390</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.7610</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.7610</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.7610</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.7610</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.7610</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.7610</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.7610</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.7610</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.8858</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.8858</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.8858</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.8858</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.8858</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.8858</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0135</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>21/08/2026</x:t>
         </x:is>
       </x:c>
